--- a/data/trending_integrated_20260914_13.xlsx
+++ b/data/trending_integrated_20260914_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G2" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>268538908395</v>
+        <v>268855655735</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 관련주로 3연상 가능성 언급. 일본 코덴시 자회사 관련 내용 포함.</t>
+          <t>차세대 광반도체 및 광통신 테마로 3연상 기대감 속에서 주포와 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', '3연상']</t>
+          <t>['광반도체', '광통신', '주포']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6470</v>
+        <v>6420</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+17.42%</t>
+          <t>+16.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>51585403600</v>
+        <v>51880576835</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4450</v>
+        <v>4350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+14.99%</t>
+          <t>+12.40%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.45</v>
       </c>
       <c r="E4" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="F4" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="H4" t="n">
         <v>0.59</v>
@@ -794,7 +794,7 @@
         <v>1.04</v>
       </c>
       <c r="O4" t="n">
-        <v>243312446854</v>
+        <v>254381071479</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9270</v>
+        <v>9250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+11.82%</t>
+          <t>+11.58%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="H5" t="n">
         <v>0.83</v>
@@ -886,7 +886,7 @@
         <v>0.82</v>
       </c>
       <c r="O5" t="n">
-        <v>38892686610</v>
+        <v>39211565140</v>
       </c>
       <c r="P5" t="n">
         <v>12800</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2815</v>
+        <v>8460</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+7.44%</t>
+          <t>+6.95%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.39</v>
+        <v>0.55</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G6" t="n">
-        <v>187</v>
+        <v>94</v>
       </c>
       <c r="H6" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2620</v>
+        <v>7910</v>
       </c>
       <c r="K6" t="n">
-        <v>2745</v>
+        <v>7800</v>
       </c>
       <c r="L6" t="n">
-        <v>3145</v>
+        <v>9840</v>
       </c>
       <c r="M6" t="n">
-        <v>2700</v>
+        <v>7540</v>
       </c>
       <c r="N6" t="n">
-        <v>3.83</v>
+        <v>0.7</v>
       </c>
       <c r="O6" t="n">
-        <v>97699147853</v>
+        <v>68263966795</v>
       </c>
       <c r="P6" t="n">
-        <v>4810</v>
+        <v>25050</v>
       </c>
       <c r="Q6" t="n">
-        <v>1400</v>
+        <v>3705</v>
       </c>
       <c r="R6" t="n">
-        <v>-240000</v>
+        <v>-24000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
+          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자 보안', '매출액', '전고점 돌파']</t>
+          <t>['펩타이드', '특허 등록', '면역 조절']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17130</v>
+        <v>2795</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.66%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.31</v>
+        <v>-2.39</v>
       </c>
       <c r="E7" t="n">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16060</v>
+        <v>2620</v>
       </c>
       <c r="K7" t="n">
-        <v>16780</v>
+        <v>2745</v>
       </c>
       <c r="L7" t="n">
-        <v>18610</v>
+        <v>3145</v>
       </c>
       <c r="M7" t="n">
-        <v>16230</v>
+        <v>2700</v>
       </c>
       <c r="N7" t="n">
-        <v>2.39</v>
+        <v>3.83</v>
       </c>
       <c r="O7" t="n">
-        <v>253225305220</v>
+        <v>97999628564</v>
       </c>
       <c r="P7" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q7" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R7" t="n">
-        <v>-292000</v>
+        <v>-240000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론에 따른 영향 분석과 함께 주가 상승 기대감. 개인 투자자 매물대 정리.</t>
+          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '속도조절론', '매물대']</t>
+          <t>['양자 보안', '매출액', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8370</v>
+        <v>8830</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.82%</t>
+          <t>+6.51%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="E8" t="n">
-        <v>62</v>
+        <v>183</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="G8" t="n">
-        <v>93</v>
+        <v>1061</v>
       </c>
       <c r="H8" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7910</v>
+        <v>8290</v>
       </c>
       <c r="K8" t="n">
-        <v>7800</v>
+        <v>8100</v>
       </c>
       <c r="L8" t="n">
-        <v>9840</v>
+        <v>9050</v>
       </c>
       <c r="M8" t="n">
-        <v>7540</v>
+        <v>8060</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>1.29</v>
       </c>
       <c r="O8" t="n">
-        <v>68075893415</v>
+        <v>27785144935</v>
       </c>
       <c r="P8" t="n">
-        <v>25050</v>
+        <v>21500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3705</v>
+        <v>2300</v>
       </c>
       <c r="R8" t="n">
-        <v>-24000</v>
+        <v>64000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
+          <t>항암 신약 관련 글로벌 심포지엄 개최 및 파텔 교수 멘토링. 빅 이벤트 기반 높은 기대감 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['펩타이드', '특허 등록', '면역 조절']</t>
+          <t>['항암신약', '심포지엄', '바이오']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14700</v>
+        <v>16970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+3.89%</t>
+          <t>+5.67%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.62</v>
+        <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="F9" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G9" t="n">
-        <v>556</v>
+        <v>173</v>
       </c>
       <c r="H9" t="n">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14150</v>
+        <v>16060</v>
       </c>
       <c r="K9" t="n">
-        <v>13850</v>
+        <v>16780</v>
       </c>
       <c r="L9" t="n">
-        <v>14950</v>
+        <v>18610</v>
       </c>
       <c r="M9" t="n">
-        <v>13800</v>
+        <v>16230</v>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="O9" t="n">
-        <v>147272722495</v>
+        <v>253950218080</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>30550</v>
       </c>
       <c r="Q9" t="n">
-        <v>1272</v>
+        <v>6100</v>
       </c>
       <c r="R9" t="n">
-        <v>-430000</v>
+        <v>-292000</v>
       </c>
       <c r="S9" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>GPU, AI 등 성장 산업 관련 광통신 기술력 부각 및 대규모 수주 기대감. 15,000원 돌파 시 추가 상승 전망.</t>
+          <t>AI 개발 속도 조절론 등락 속에서 2연상 기대감 및 17층 매물대 정리 시도.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '수주']</t>
+          <t>['AI', '2연상', '속도조절론']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21900</v>
+        <v>14680</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.34%</t>
+          <t>+3.75%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.08</v>
+        <v>-0.62</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>171</v>
       </c>
       <c r="F10" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="G10" t="n">
-        <v>244</v>
+        <v>577</v>
       </c>
       <c r="H10" t="n">
-        <v>28.81</v>
+        <v>1.88</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>21400</v>
+        <v>14150</v>
       </c>
       <c r="K10" t="n">
-        <v>21100</v>
+        <v>13850</v>
       </c>
       <c r="L10" t="n">
-        <v>21950</v>
+        <v>14950</v>
       </c>
       <c r="M10" t="n">
-        <v>20850</v>
+        <v>13800</v>
       </c>
       <c r="N10" t="n">
-        <v>28.89</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>40381205675</v>
+        <v>151553645765</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>18440</v>
+        <v>1272</v>
       </c>
       <c r="R10" t="n">
-        <v>86000</v>
+        <v>-430000</v>
       </c>
       <c r="S10" t="n">
-        <v>-15000</v>
+        <v>-1000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>LNG·원유운반선 총 6척 수주(1.6조원) 공시 확인. 조선업 호황 속 쇄빙선, LNG선 등 신규 사업 기대.</t>
+          <t>AIDC 광통신 기술력 기반으로 GPU 확보와 연결, 15000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', '조선업', 'LNG선']</t>
+          <t>['광통신', 'AIDC', 'GPU']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14890</v>
+        <v>21900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>+2.34%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.97</v>
+        <v>-0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>275</v>
+        <v>92</v>
       </c>
       <c r="F11" t="n">
-        <v>156</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>700</v>
+        <v>249</v>
       </c>
       <c r="H11" t="n">
-        <v>1.17</v>
+        <v>28.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14610</v>
+        <v>21400</v>
       </c>
       <c r="K11" t="n">
-        <v>15420</v>
+        <v>21100</v>
       </c>
       <c r="L11" t="n">
-        <v>16510</v>
+        <v>21950</v>
       </c>
       <c r="M11" t="n">
-        <v>14320</v>
+        <v>20850</v>
       </c>
       <c r="N11" t="n">
-        <v>3.14</v>
+        <v>28.89</v>
       </c>
       <c r="O11" t="n">
-        <v>104757192680</v>
+        <v>43214154075</v>
       </c>
       <c r="P11" t="n">
-        <v>36200</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>8920</v>
+        <v>18440</v>
       </c>
       <c r="R11" t="n">
-        <v>-128000</v>
+        <v>86000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>이란-걸프국 회담 연기 및 국제유가 폭등 관련 수혜 기대감. 단기 급등락 반복.</t>
+          <t>LNG선 등 대규모 수주 공시와 조선업 호황 기대감 속에 2.63억 달러 규모 수주 확인.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '회담연기']</t>
+          <t>['수주', '조선업', 'LNG선']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8370</v>
+        <v>14810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.54</v>
+        <v>-1.97</v>
       </c>
       <c r="E12" t="n">
-        <v>174</v>
+        <v>283</v>
       </c>
       <c r="F12" t="n">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="G12" t="n">
-        <v>1004</v>
+        <v>709</v>
       </c>
       <c r="H12" t="n">
-        <v>0.75</v>
+        <v>1.17</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8290</v>
+        <v>14610</v>
       </c>
       <c r="K12" t="n">
-        <v>8100</v>
+        <v>15420</v>
       </c>
       <c r="L12" t="n">
-        <v>9050</v>
+        <v>16510</v>
       </c>
       <c r="M12" t="n">
-        <v>8060</v>
+        <v>14320</v>
       </c>
       <c r="N12" t="n">
-        <v>1.29</v>
+        <v>3.14</v>
       </c>
       <c r="O12" t="n">
-        <v>23587374000</v>
+        <v>105289415080</v>
       </c>
       <c r="P12" t="n">
-        <v>21500</v>
+        <v>36200</v>
       </c>
       <c r="Q12" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R12" t="n">
-        <v>64000</v>
+        <v>-128000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>항암 신약 관련 글로벌 심포지엄 개최 및 파텔 교수 멘토링. 빅 이벤트 기반 높은 기대감 형성.</t>
+          <t>이란-걸프국 회담 연기 및 국제유가 폭등 관련 수혜 기대감. 단기 급등락 반복.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['항암신약', '심포지엄', '바이오']</t>
+          <t>['국제유가', '호르무즈', '회담연기']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1579,18 +1579,18 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.36</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F13" t="n">
         <v>39</v>
@@ -1622,7 +1622,7 @@
         <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>15598347857</v>
+        <v>15652351871</v>
       </c>
       <c r="P13" t="n">
         <v>4795</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>251750</v>
+        <v>251500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.99%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G14" t="n">
-        <v>1716</v>
+        <v>1729</v>
       </c>
       <c r="H14" t="n">
         <v>46.64</v>
@@ -1714,7 +1714,7 @@
         <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2503551370000</v>
+        <v>2558320197000</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88000</v>
+        <v>87800</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-3.30%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F15" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G15" t="n">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="H15" t="n">
         <v>23.56</v>
@@ -1806,7 +1806,7 @@
         <v>23.59</v>
       </c>
       <c r="O15" t="n">
-        <v>157560807650</v>
+        <v>160311501000</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>국제 유가 상승 수혜 기대감 속 원전주 상승 가능성 언급. 공매도 세력과의 차익 실현 공방 예상.</t>
+          <t>국제 유가 상승과 한미 정부 지원 속에서 원전주로서의 상승 가능성 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['국제유가', '원전주', '공매도']</t>
+          <t>['원전', '유가', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11780</v>
+        <v>11800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.15%</t>
+          <t>-3.99%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.72</v>
       </c>
       <c r="E16" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H16" t="n">
         <v>0.22</v>
@@ -1898,7 +1898,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>55894825915</v>
+        <v>56096957405</v>
       </c>
       <c r="P16" t="n">
         <v>20850</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18890</v>
+        <v>18820</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.03%</t>
+          <t>-5.38%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="H17" t="n">
         <v>10.55</v>
@@ -1990,7 +1990,7 @@
         <v>10.65</v>
       </c>
       <c r="O17" t="n">
-        <v>57504335155</v>
+        <v>59078143925</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대차 해지 운동 및 공매도 세력과의 대립 구도 형성. 저점 매수 기회 및 주가 반등 기대감 언급, 투자자 참여 독려.</t>
+          <t>대차해지 운동 독려와 개미 뭉치기 주장에도 불구하고 주가 하락세.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '반등 기대']</t>
+          <t>['대차해지', '공매도', '개미']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1716000</v>
+        <v>1712000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.30%</t>
+          <t>-5.52%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="G18" t="n">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="H18" t="n">
         <v>50.47</v>
@@ -2082,7 +2082,7 @@
         <v>50.55</v>
       </c>
       <c r="O18" t="n">
-        <v>4133593380500</v>
+        <v>4240540851000</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미금리 인상 불확실성 해소 기대와 달리 하락 추세, 개미 투자자들의 어려움 언급.</t>
+          <t>미 금리 인상 불확실성 속에서 하락세 지속, 일부 투자자는 장투 및 추매 고려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['반도체', '미금리', '하락']</t>
+          <t>['금리', '반도체', '장투']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13790</v>
+        <v>13850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.25%</t>
+          <t>-5.85%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
         <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>27615171540</v>
+        <v>27888712580</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11380</v>
+        <v>11480</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-8.59%</t>
+          <t>-7.79%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.51</v>
       </c>
       <c r="E20" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G20" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H20" t="n">
         <v>17.58</v>
@@ -2266,7 +2266,7 @@
         <v>17.07</v>
       </c>
       <c r="O20" t="n">
-        <v>61890021675</v>
+        <v>62481254975</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>단타 및 수급 싸움 양상 속 급등락 반복, 외인 매수 후 매도 관찰.</t>
+          <t>외인 대량 매수세 관찰되나, 투자경고 가능성 및 급락 움직임 혼재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['단타', '수급', '외인']</t>
+          <t>['외인', '수급', '투자경고']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20260914_13.xlsx
+++ b/data/trending_integrated_20260914_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G2" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>268855655735</v>
+        <v>269219480755</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -619,23 +619,23 @@
         <v>1760</v>
       </c>
       <c r="R2" t="n">
-        <v>1000</v>
+        <v>-15000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 테마로 3연상 기대감 속에서 주포와 프로그램 매수세 유입.</t>
+          <t>차세대 광반도체 및 광통신 관련주로 언급되며 3연상 기대감 표출. 단기 시세 끝 및 급락장 주의 언급도 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', '주포']</t>
+          <t>['광반도체', '광통신', '3연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6420</v>
+        <v>6480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+16.52%</t>
+          <t>+17.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>51880576835</v>
+        <v>52137861240</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -711,7 +711,7 @@
         <v>2965</v>
       </c>
       <c r="R3" t="n">
-        <v>-77000</v>
+        <v>-63000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4350</v>
+        <v>4415</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+12.40%</t>
+          <t>+14.08%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.45</v>
       </c>
       <c r="E4" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G4" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H4" t="n">
         <v>0.59</v>
@@ -794,7 +794,7 @@
         <v>1.04</v>
       </c>
       <c r="O4" t="n">
-        <v>254381071479</v>
+        <v>263810343179</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -803,23 +803,23 @@
         <v>592</v>
       </c>
       <c r="R4" t="n">
-        <v>-217000</v>
+        <v>-161000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술 및 6G 시대 관련주로 부각, 국책사업 선정 기대감 형성.</t>
+          <t>6G 시대 도래 및 AIDC 광통신 기술 관련 기대감. 국책사업 선정 및 텐버거 종목 가능성 언급. 투자경고 언급도 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', '6G', '국책사업']</t>
+          <t>['6G', '광통신', '국책사업']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9250</v>
+        <v>9240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+11.58%</t>
+          <t>+11.46%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H5" t="n">
         <v>0.83</v>
@@ -886,7 +886,7 @@
         <v>0.82</v>
       </c>
       <c r="O5" t="n">
-        <v>39211565140</v>
+        <v>39722133760</v>
       </c>
       <c r="P5" t="n">
         <v>12800</v>
@@ -895,10 +895,10 @@
         <v>5340</v>
       </c>
       <c r="R5" t="n">
-        <v>447000</v>
+        <v>507000</v>
       </c>
       <c r="S5" t="n">
-        <v>127000</v>
+        <v>109000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8460</v>
+        <v>2820</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+6.95%</t>
+          <t>+7.63%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.55</v>
+        <v>-2.39</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>94</v>
+        <v>213</v>
       </c>
       <c r="H6" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7910</v>
+        <v>2620</v>
       </c>
       <c r="K6" t="n">
-        <v>7800</v>
+        <v>2745</v>
       </c>
       <c r="L6" t="n">
-        <v>9840</v>
+        <v>3145</v>
       </c>
       <c r="M6" t="n">
-        <v>7540</v>
+        <v>2700</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7</v>
+        <v>3.83</v>
       </c>
       <c r="O6" t="n">
-        <v>68263966795</v>
+        <v>98576545803</v>
       </c>
       <c r="P6" t="n">
-        <v>25050</v>
+        <v>4810</v>
       </c>
       <c r="Q6" t="n">
-        <v>3705</v>
+        <v>1400</v>
       </c>
       <c r="R6" t="n">
-        <v>-24000</v>
+        <v>-275000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
+          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['펩타이드', '특허 등록', '면역 조절']</t>
+          <t>['양자 보안', '매출액', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2795</v>
+        <v>17170</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>+6.91%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-2.39</v>
+        <v>0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="G7" t="n">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="H7" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2620</v>
+        <v>16060</v>
       </c>
       <c r="K7" t="n">
-        <v>2745</v>
+        <v>16780</v>
       </c>
       <c r="L7" t="n">
-        <v>3145</v>
+        <v>18610</v>
       </c>
       <c r="M7" t="n">
-        <v>2700</v>
+        <v>16230</v>
       </c>
       <c r="N7" t="n">
-        <v>3.83</v>
+        <v>2.39</v>
       </c>
       <c r="O7" t="n">
-        <v>97999628564</v>
+        <v>256373591730</v>
       </c>
       <c r="P7" t="n">
-        <v>4810</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>1400</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>-240000</v>
+        <v>-281000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
+          <t>AI 개발 속도 조절론에 따른 영향 분석과 함께 주가 상승 기대감. 개인 투자자 매물대 정리.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자 보안', '매출액', '전고점 돌파']</t>
+          <t>['AI', '속도조절론', '매물대']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8830</v>
+        <v>8450</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.51%</t>
+          <t>+6.83%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.54</v>
+        <v>0.55</v>
       </c>
       <c r="E8" t="n">
-        <v>183</v>
+        <v>62</v>
       </c>
       <c r="F8" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>1061</v>
+        <v>94</v>
       </c>
       <c r="H8" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>8290</v>
+        <v>7910</v>
       </c>
       <c r="K8" t="n">
-        <v>8100</v>
+        <v>7800</v>
       </c>
       <c r="L8" t="n">
-        <v>9050</v>
+        <v>9840</v>
       </c>
       <c r="M8" t="n">
-        <v>8060</v>
+        <v>7540</v>
       </c>
       <c r="N8" t="n">
-        <v>1.29</v>
+        <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>27785144935</v>
+        <v>68690325725</v>
       </c>
       <c r="P8" t="n">
-        <v>21500</v>
+        <v>25050</v>
       </c>
       <c r="Q8" t="n">
-        <v>2300</v>
+        <v>3705</v>
       </c>
       <c r="R8" t="n">
-        <v>64000</v>
+        <v>19000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>항암 신약 관련 글로벌 심포지엄 개최 및 파텔 교수 멘토링. 빅 이벤트 기반 높은 기대감 형성.</t>
+          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['항암신약', '심포지엄', '바이오']</t>
+          <t>['펩타이드', '특허 등록', '면역 조절']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16970</v>
+        <v>8600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.67%</t>
+          <t>+3.74%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.31</v>
+        <v>-0.54</v>
       </c>
       <c r="E9" t="n">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="F9" t="n">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="G9" t="n">
-        <v>173</v>
+        <v>1133</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7</v>
+        <v>0.75</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>16060</v>
+        <v>8290</v>
       </c>
       <c r="K9" t="n">
-        <v>16780</v>
+        <v>8100</v>
       </c>
       <c r="L9" t="n">
-        <v>18610</v>
+        <v>9050</v>
       </c>
       <c r="M9" t="n">
-        <v>16230</v>
+        <v>8060</v>
       </c>
       <c r="N9" t="n">
-        <v>2.39</v>
+        <v>1.29</v>
       </c>
       <c r="O9" t="n">
-        <v>253950218080</v>
+        <v>29256333255</v>
       </c>
       <c r="P9" t="n">
-        <v>30550</v>
+        <v>21500</v>
       </c>
       <c r="Q9" t="n">
-        <v>6100</v>
+        <v>2300</v>
       </c>
       <c r="R9" t="n">
-        <v>-292000</v>
+        <v>-43000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론 등락 속에서 2연상 기대감 및 17층 매물대 정리 시도.</t>
+          <t>항암 신약 관련 글로벌 심포지엄 개최 및 파텔 교수 멘토링. 빅 이벤트 기반 높은 기대감 형성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '2연상', '속도조절론']</t>
+          <t>['항암신약', '심포지엄', '바이오']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14680</v>
+        <v>22150</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.75%</t>
+          <t>+3.50%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.62</v>
+        <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>171</v>
+        <v>91</v>
       </c>
       <c r="F10" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="G10" t="n">
-        <v>577</v>
+        <v>259</v>
       </c>
       <c r="H10" t="n">
-        <v>1.88</v>
+        <v>28.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14150</v>
+        <v>21400</v>
       </c>
       <c r="K10" t="n">
-        <v>13850</v>
+        <v>21100</v>
       </c>
       <c r="L10" t="n">
-        <v>14950</v>
+        <v>22150</v>
       </c>
       <c r="M10" t="n">
-        <v>13800</v>
+        <v>20850</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>151553645765</v>
+        <v>48386364575</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>1272</v>
+        <v>18440</v>
       </c>
       <c r="R10" t="n">
-        <v>-430000</v>
+        <v>368000</v>
       </c>
       <c r="S10" t="n">
-        <v>-1000</v>
+        <v>36000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술력 기반으로 GPU 확보와 연결, 15000원 돌파 기대.</t>
+          <t>대차거래 잔고 감소 및 숏커버 가능성 언급. LNG선, 해상 데이터센터 수주 등 호황 전망 및 1.6조원 규모 수주 공시 확인.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', 'GPU']</t>
+          <t>['수주', 'LNG선', '대차거래']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21900</v>
+        <v>14640</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.34%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.08</v>
+        <v>-0.62</v>
       </c>
       <c r="E11" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F11" t="n">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="G11" t="n">
-        <v>249</v>
+        <v>610</v>
       </c>
       <c r="H11" t="n">
-        <v>28.81</v>
+        <v>1.88</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>21400</v>
+        <v>14150</v>
       </c>
       <c r="K11" t="n">
-        <v>21100</v>
+        <v>13850</v>
       </c>
       <c r="L11" t="n">
-        <v>21950</v>
+        <v>14950</v>
       </c>
       <c r="M11" t="n">
-        <v>20850</v>
+        <v>13800</v>
       </c>
       <c r="N11" t="n">
-        <v>28.89</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>43214154075</v>
+        <v>155632851580</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>18440</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>86000</v>
+        <v>-407000</v>
       </c>
       <c r="S11" t="n">
-        <v>-15000</v>
+        <v>-2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>LNG선 등 대규모 수주 공시와 조선업 호황 기대감 속에 2.63억 달러 규모 수주 확인.</t>
+          <t>AI 및 광통신 기술 관련 호재 언급. 광통신 대장주 및 15000원 돌파 기대감 표출. 프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주', '조선업', 'LNG선']</t>
+          <t>['광통신', 'AI', '프로그램매수']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14810</v>
+        <v>14770</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.37%</t>
+          <t>+1.10%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-1.97</v>
       </c>
       <c r="E12" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F12" t="n">
         <v>156</v>
       </c>
       <c r="G12" t="n">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H12" t="n">
         <v>1.17</v>
@@ -1530,7 +1530,7 @@
         <v>3.14</v>
       </c>
       <c r="O12" t="n">
-        <v>105289415080</v>
+        <v>105649103460</v>
       </c>
       <c r="P12" t="n">
         <v>36200</v>
@@ -1539,7 +1539,7 @@
         <v>8920</v>
       </c>
       <c r="R12" t="n">
-        <v>-128000</v>
+        <v>-108000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1867</v>
+        <v>1861</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H13" t="n">
         <v>2.08</v>
@@ -1622,7 +1622,7 @@
         <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>15652351871</v>
+        <v>15756999569</v>
       </c>
       <c r="P13" t="n">
         <v>4795</v>
@@ -1631,7 +1631,7 @@
         <v>1524</v>
       </c>
       <c r="R13" t="n">
-        <v>-224000</v>
+        <v>-273000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>251500</v>
+        <v>87900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>218</v>
       </c>
       <c r="F14" t="n">
-        <v>490</v>
+        <v>124</v>
       </c>
       <c r="G14" t="n">
-        <v>1729</v>
+        <v>713</v>
       </c>
       <c r="H14" t="n">
-        <v>46.64</v>
+        <v>23.56</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>259500</v>
+        <v>90800</v>
       </c>
       <c r="K14" t="n">
-        <v>249500</v>
+        <v>89800</v>
       </c>
       <c r="L14" t="n">
-        <v>254500</v>
+        <v>90400</v>
       </c>
       <c r="M14" t="n">
-        <v>249000</v>
+        <v>87700</v>
       </c>
       <c r="N14" t="n">
-        <v>46.71</v>
+        <v>23.59</v>
       </c>
       <c r="O14" t="n">
-        <v>2558320197000</v>
+        <v>164342996650</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>75900</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-2179000</v>
+        <v>-546000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1014000</v>
+        <v>-91000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대통령 선거 결과에 따른 주가 전망 언급. 정치적 이슈가 주가에 영향을 미칠 것이라는 기대감과 부정적 전망이 혼재.</t>
+          <t>국제 유가 상승과 한미 정부 지원 속에서 원전주로서의 상승 가능성 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대통령', '선거', '주가전망']</t>
+          <t>['원전', '유가', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87800</v>
+        <v>251000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.30%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>214</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>120</v>
+        <v>484</v>
       </c>
       <c r="G15" t="n">
-        <v>709</v>
+        <v>1741</v>
       </c>
       <c r="H15" t="n">
-        <v>23.56</v>
+        <v>46.64</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>90800</v>
+        <v>259500</v>
       </c>
       <c r="K15" t="n">
-        <v>89800</v>
+        <v>249500</v>
       </c>
       <c r="L15" t="n">
-        <v>90400</v>
+        <v>254500</v>
       </c>
       <c r="M15" t="n">
-        <v>87700</v>
+        <v>249000</v>
       </c>
       <c r="N15" t="n">
-        <v>23.59</v>
+        <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>160311501000</v>
+        <v>2636454357000</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>75900</v>
       </c>
       <c r="R15" t="n">
-        <v>-464000</v>
+        <v>-2691000</v>
       </c>
       <c r="S15" t="n">
-        <v>-70000</v>
+        <v>-1229000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>국제 유가 상승과 한미 정부 지원 속에서 원전주로서의 상승 가능성 기대.</t>
+          <t>정치적 이슈와 연관된 언급이 다수. AI 속도 조절론 및 외국인 공매도 관련 부정적 전망 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', '유가', '공매도']</t>
+          <t>['AI', '공매도', '정치']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11800</v>
+        <v>11770</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.99%</t>
+          <t>-4.23%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.72</v>
       </c>
       <c r="E16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H16" t="n">
         <v>0.22</v>
@@ -1892,13 +1892,13 @@
         <v>13230</v>
       </c>
       <c r="M16" t="n">
-        <v>11750</v>
+        <v>11740</v>
       </c>
       <c r="N16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>56096957405</v>
+        <v>56259693655</v>
       </c>
       <c r="P16" t="n">
         <v>20850</v>
@@ -1907,7 +1907,7 @@
         <v>4020</v>
       </c>
       <c r="R16" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18820</v>
+        <v>1712000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.38%</t>
+          <t>-5.52%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>492</v>
       </c>
       <c r="G17" t="n">
-        <v>364</v>
+        <v>1601</v>
       </c>
       <c r="H17" t="n">
-        <v>10.55</v>
+        <v>50.47</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>19890</v>
+        <v>1812000</v>
       </c>
       <c r="K17" t="n">
-        <v>19480</v>
+        <v>1707000</v>
       </c>
       <c r="L17" t="n">
-        <v>19550</v>
+        <v>1740000</v>
       </c>
       <c r="M17" t="n">
-        <v>18780</v>
+        <v>1695000</v>
       </c>
       <c r="N17" t="n">
-        <v>10.65</v>
+        <v>50.55</v>
       </c>
       <c r="O17" t="n">
-        <v>59078143925</v>
+        <v>4343182412500</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>325000</v>
       </c>
       <c r="R17" t="n">
-        <v>-430000</v>
+        <v>-1020000</v>
       </c>
       <c r="S17" t="n">
-        <v>-48000</v>
+        <v>-202000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대차해지 운동 독려와 개미 뭉치기 주장에도 불구하고 주가 하락세.</t>
+          <t>외국인 선물 매수 전환에도 불구하고 금리 인상 및 정치적 이슈 관련 부정적 전망 우세. 큰 폭의 하락 우려 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '개미']</t>
+          <t>['금리', '외국인', '하락']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1712000</v>
+        <v>18760</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.52%</t>
+          <t>-5.68%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>83</v>
       </c>
       <c r="F18" t="n">
-        <v>490</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>1602</v>
+        <v>388</v>
       </c>
       <c r="H18" t="n">
-        <v>50.47</v>
+        <v>10.55</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1812000</v>
+        <v>19890</v>
       </c>
       <c r="K18" t="n">
-        <v>1707000</v>
+        <v>19480</v>
       </c>
       <c r="L18" t="n">
-        <v>1740000</v>
+        <v>19550</v>
       </c>
       <c r="M18" t="n">
-        <v>1695000</v>
+        <v>18750</v>
       </c>
       <c r="N18" t="n">
-        <v>50.55</v>
+        <v>10.65</v>
       </c>
       <c r="O18" t="n">
-        <v>4240540851000</v>
+        <v>62420759585</v>
       </c>
       <c r="P18" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>325000</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-897000</v>
+        <v>-480000</v>
       </c>
       <c r="S18" t="n">
-        <v>-147000</v>
+        <v>-158000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미 금리 인상 불확실성 속에서 하락세 지속, 일부 투자자는 장투 및 추매 고려.</t>
+          <t>대차해지 운동 참여 독려 글이 다수. 개미 뭉치를 통한 공매도 작살 및 저점 높아지는 추세 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['금리', '반도체', '장투']</t>
+          <t>['대차해지', '공매도', '뭉치']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13850</v>
+        <v>13800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.85%</t>
+          <t>-6.19%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>27888712580</v>
+        <v>28139603385</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2183,7 +2183,7 @@
         <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>-67000</v>
+        <v>-60000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11480</v>
+        <v>11390</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-7.79%</t>
+          <t>-8.51%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.51</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G20" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="H20" t="n">
         <v>17.58</v>
@@ -2266,7 +2266,7 @@
         <v>17.07</v>
       </c>
       <c r="O20" t="n">
-        <v>62481254975</v>
+        <v>63099342595</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2275,23 +2275,23 @@
         <v>465</v>
       </c>
       <c r="R20" t="n">
-        <v>-51000</v>
+        <v>-140000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>외인 대량 매수세 관찰되나, 투자경고 가능성 및 급락 움직임 혼재.</t>
+          <t>외국인 대량 매수 포착 및 급등주 언급. 수급 싸움 및 외인 매도 가능성도 제기.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['외인', '수급', '투자경고']</t>
+          <t>['외국인', '급등주', '수급']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20260914_13.xlsx
+++ b/data/trending_integrated_20260914_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>269219480755</v>
+        <v>269618038915</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 관련주로 언급되며 3연상 기대감 표출. 단기 시세 끝 및 급락장 주의 언급도 존재.</t>
+          <t>차세대 광반도체 및 광통신 테마 부각, 3연상 기대감 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6480</v>
+        <v>6420</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+17.60%</t>
+          <t>+16.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F3" t="n">
         <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>52137861240</v>
+        <v>52302187160</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한국비엔씨</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4415</v>
+        <v>2945</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+14.08%</t>
+          <t>+13.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.45</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>220</v>
+        <v>61</v>
       </c>
       <c r="H4" t="n">
-        <v>0.59</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3870</v>
+        <v>2585</v>
       </c>
       <c r="K4" t="n">
-        <v>3860</v>
+        <v>2530</v>
       </c>
       <c r="L4" t="n">
-        <v>4620</v>
+        <v>3095</v>
       </c>
       <c r="M4" t="n">
-        <v>3740</v>
+        <v>2520</v>
       </c>
       <c r="N4" t="n">
-        <v>1.04</v>
+        <v>3.64</v>
       </c>
       <c r="O4" t="n">
-        <v>263810343179</v>
+        <v>36559476167</v>
       </c>
       <c r="P4" t="n">
-        <v>8100</v>
+        <v>6180</v>
       </c>
       <c r="Q4" t="n">
-        <v>592</v>
+        <v>2050</v>
       </c>
       <c r="R4" t="n">
-        <v>-161000</v>
+        <v>109000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>6G 시대 도래 및 AIDC 광통신 기술 관련 기대감. 국책사업 선정 및 텐버거 종목 가능성 언급. 투자경고 언급도 존재.</t>
+          <t>FDA 비만 주사제 관련 기대감과 5500억 계약 건 언급. 3상 시작 전 FDA 승인 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['6G', '광통신', '국책사업']</t>
+          <t>['FDA', '비만주사제', '계약']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>256840</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9240</v>
+        <v>4325</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+11.46%</t>
+          <t>+11.76%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01</v>
+        <v>-0.45</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="H5" t="n">
-        <v>0.83</v>
+        <v>0.59</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,91 +871,91 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8290</v>
+        <v>3870</v>
       </c>
       <c r="K5" t="n">
-        <v>8300</v>
+        <v>3860</v>
       </c>
       <c r="L5" t="n">
-        <v>9440</v>
+        <v>4620</v>
       </c>
       <c r="M5" t="n">
-        <v>8300</v>
+        <v>3740</v>
       </c>
       <c r="N5" t="n">
-        <v>0.82</v>
+        <v>1.04</v>
       </c>
       <c r="O5" t="n">
-        <v>39722133760</v>
+        <v>270142025726</v>
       </c>
       <c r="P5" t="n">
-        <v>12800</v>
+        <v>8100</v>
       </c>
       <c r="Q5" t="n">
-        <v>5340</v>
+        <v>592</v>
       </c>
       <c r="R5" t="n">
-        <v>507000</v>
+        <v>-161000</v>
       </c>
       <c r="S5" t="n">
-        <v>109000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>폴더블폰 시장 확대에 따른 수혜 기대감, 그러나 단기 차익 실현 및 전환사채 관련 이슈로 인한 변동성.</t>
+          <t>AIDC, 6G, 광통신 기술 부각 및 광전자 급등세 영향. 5000원 안착 시 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['폴더블', '매출 증', '전환사채']</t>
+          <t>['AIDC', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2820</v>
+        <v>9170</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+7.63%</t>
+          <t>+10.62%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.39</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="H6" t="n">
-        <v>1.44</v>
+        <v>0.83</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2620</v>
+        <v>8290</v>
       </c>
       <c r="K6" t="n">
-        <v>2745</v>
+        <v>8300</v>
       </c>
       <c r="L6" t="n">
-        <v>3145</v>
+        <v>9440</v>
       </c>
       <c r="M6" t="n">
-        <v>2700</v>
+        <v>8300</v>
       </c>
       <c r="N6" t="n">
-        <v>3.83</v>
+        <v>0.82</v>
       </c>
       <c r="O6" t="n">
-        <v>98576545803</v>
+        <v>41226363390</v>
       </c>
       <c r="P6" t="n">
-        <v>4810</v>
+        <v>12800</v>
       </c>
       <c r="Q6" t="n">
-        <v>1400</v>
+        <v>5340</v>
       </c>
       <c r="R6" t="n">
-        <v>-275000</v>
+        <v>507000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>109000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
+          <t>폴더블폰 시장 확대에 따른 수혜 기대감, 그러나 단기 차익 실현 및 전환사채 관련 이슈로 인한 변동성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자 보안', '매출액', '전고점 돌파']</t>
+          <t>['폴더블', '매출 증', '전환사채']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>441270</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17170</v>
+        <v>2800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.91%</t>
+          <t>+6.87%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.31</v>
+        <v>-2.39</v>
       </c>
       <c r="E7" t="n">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16060</v>
+        <v>2620</v>
       </c>
       <c r="K7" t="n">
-        <v>16780</v>
+        <v>2745</v>
       </c>
       <c r="L7" t="n">
-        <v>18610</v>
+        <v>3145</v>
       </c>
       <c r="M7" t="n">
-        <v>16230</v>
+        <v>2700</v>
       </c>
       <c r="N7" t="n">
-        <v>2.39</v>
+        <v>3.83</v>
       </c>
       <c r="O7" t="n">
-        <v>256373591730</v>
+        <v>98788854928</v>
       </c>
       <c r="P7" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q7" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R7" t="n">
-        <v>-281000</v>
+        <v>-275000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론에 따른 영향 분석과 함께 주가 상승 기대감. 개인 투자자 매물대 정리.</t>
+          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '속도조절론', '매물대']</t>
+          <t>['양자 보안', '매출액', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>8380</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.83%</t>
+          <t>+5.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1162,7 +1162,7 @@
         <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>68690325725</v>
+        <v>68847014370</v>
       </c>
       <c r="P8" t="n">
         <v>25050</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8600</v>
+        <v>16930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+3.74%</t>
+          <t>+5.42%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.54</v>
+        <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>198</v>
+        <v>122</v>
       </c>
       <c r="F9" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>1133</v>
+        <v>183</v>
       </c>
       <c r="H9" t="n">
-        <v>0.75</v>
+        <v>2.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8290</v>
+        <v>16060</v>
       </c>
       <c r="K9" t="n">
-        <v>8100</v>
+        <v>16780</v>
       </c>
       <c r="L9" t="n">
-        <v>9050</v>
+        <v>18610</v>
       </c>
       <c r="M9" t="n">
-        <v>8060</v>
+        <v>16230</v>
       </c>
       <c r="N9" t="n">
-        <v>1.29</v>
+        <v>2.39</v>
       </c>
       <c r="O9" t="n">
-        <v>29256333255</v>
+        <v>257574234265</v>
       </c>
       <c r="P9" t="n">
-        <v>21500</v>
+        <v>30550</v>
       </c>
       <c r="Q9" t="n">
-        <v>2300</v>
+        <v>6100</v>
       </c>
       <c r="R9" t="n">
-        <v>-43000</v>
+        <v>-281000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>항암 신약 관련 글로벌 심포지엄 개최 및 파텔 교수 멘토링. 빅 이벤트 기반 높은 기대감 형성.</t>
+          <t>AI 개발 속도 조절론에 따른 영향 및 프로그램 매도세 관찰. 2연상 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['항암신약', '심포지엄', '바이오']</t>
+          <t>['AI', '속도조절론', '프로그램매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22150</v>
+        <v>22175</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.50%</t>
+          <t>+3.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G10" t="n">
-        <v>259</v>
+        <v>310</v>
       </c>
       <c r="H10" t="n">
         <v>28.81</v>
@@ -1337,7 +1337,7 @@
         <v>21100</v>
       </c>
       <c r="L10" t="n">
-        <v>22150</v>
+        <v>22200</v>
       </c>
       <c r="M10" t="n">
         <v>20850</v>
@@ -1346,7 +1346,7 @@
         <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>48386364575</v>
+        <v>51850889950</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대차거래 잔고 감소 및 숏커버 가능성 언급. LNG선, 해상 데이터센터 수주 등 호황 전망 및 1.6조원 규모 수주 공시 확인.</t>
+          <t>대형 상선 수주 성공 및 1.6조원 규모 계약 확인. 숏커버 및 공매도 관련 논의.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', 'LNG선', '대차거래']</t>
+          <t>['수주', '상선', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14640</v>
+        <v>14570</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.46%</t>
+          <t>+2.97%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.62</v>
       </c>
       <c r="E11" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F11" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G11" t="n">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="H11" t="n">
         <v>1.88</v>
@@ -1438,7 +1438,7 @@
         <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>155632851580</v>
+        <v>157357283710</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14770</v>
+        <v>8520</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.10%</t>
+          <t>+2.77%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.97</v>
+        <v>-0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>281</v>
+        <v>205</v>
       </c>
       <c r="F12" t="n">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="G12" t="n">
-        <v>708</v>
+        <v>1172</v>
       </c>
       <c r="H12" t="n">
-        <v>1.17</v>
+        <v>0.75</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14610</v>
+        <v>8290</v>
       </c>
       <c r="K12" t="n">
-        <v>15420</v>
+        <v>8100</v>
       </c>
       <c r="L12" t="n">
-        <v>16510</v>
+        <v>9050</v>
       </c>
       <c r="M12" t="n">
-        <v>14320</v>
+        <v>8060</v>
       </c>
       <c r="N12" t="n">
-        <v>3.14</v>
+        <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>105649103460</v>
+        <v>30156920885</v>
       </c>
       <c r="P12" t="n">
-        <v>36200</v>
+        <v>21500</v>
       </c>
       <c r="Q12" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R12" t="n">
-        <v>-108000</v>
+        <v>-43000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>이란-걸프국 회담 연기 및 국제유가 폭등 관련 수혜 기대감. 단기 급등락 반복.</t>
+          <t>글로벌 심포지엄 개최 기사 언급. 탑급 교수 발표와 항암 신약 재료 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '회담연기']</t>
+          <t>['항암', '심포지엄', '신약']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,130 +1568,130 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1861</v>
+        <v>14750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.36</v>
+        <v>-1.97</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>282</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="G13" t="n">
-        <v>229</v>
+        <v>715</v>
       </c>
       <c r="H13" t="n">
-        <v>2.08</v>
+        <v>1.17</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1878</v>
+        <v>14610</v>
       </c>
       <c r="K13" t="n">
-        <v>1909</v>
+        <v>15420</v>
       </c>
       <c r="L13" t="n">
-        <v>1961</v>
+        <v>16510</v>
       </c>
       <c r="M13" t="n">
-        <v>1840</v>
+        <v>14320</v>
       </c>
       <c r="N13" t="n">
-        <v>2.44</v>
+        <v>3.14</v>
       </c>
       <c r="O13" t="n">
-        <v>15756999569</v>
+        <v>105912846005</v>
       </c>
       <c r="P13" t="n">
-        <v>4795</v>
+        <v>36200</v>
       </c>
       <c r="Q13" t="n">
-        <v>1524</v>
+        <v>8920</v>
       </c>
       <c r="R13" t="n">
-        <v>-273000</v>
+        <v>-108000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유가 상승 및 중동 불안 심화로 인한 운임 강세 기대에도 불구하고, 해운주 전반의 악재 및 매수세 부진으로 주가 부진. 원가 상승 우려.</t>
+          <t>이란-걸프국 회담 연기 및 국제유가 폭등 관련 수혜 기대감. 단기 급등락 반복.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유가', '운임', '중동 불안']</t>
+          <t>['국제유가', '호르무즈', '회담연기']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>87900</v>
+        <v>1862</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.03</v>
+        <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>218</v>
+        <v>61</v>
       </c>
       <c r="F14" t="n">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="G14" t="n">
-        <v>713</v>
+        <v>229</v>
       </c>
       <c r="H14" t="n">
-        <v>23.56</v>
+        <v>2.08</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>90800</v>
+        <v>1878</v>
       </c>
       <c r="K14" t="n">
-        <v>89800</v>
+        <v>1909</v>
       </c>
       <c r="L14" t="n">
-        <v>90400</v>
+        <v>1961</v>
       </c>
       <c r="M14" t="n">
-        <v>87700</v>
+        <v>1840</v>
       </c>
       <c r="N14" t="n">
-        <v>23.59</v>
+        <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>164342996650</v>
+        <v>15831201889</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>4795</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>1524</v>
       </c>
       <c r="R14" t="n">
-        <v>-546000</v>
+        <v>-273000</v>
       </c>
       <c r="S14" t="n">
-        <v>-91000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국제 유가 상승과 한미 정부 지원 속에서 원전주로서의 상승 가능성 기대.</t>
+          <t>유가 상승 및 중동 불안 심화로 인한 운임 강세 기대에도 불구하고, 해운주 전반의 악재 및 매수세 부진으로 주가 부진. 원가 상승 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '유가', '공매도']</t>
+          <t>['유가', '운임', '중동 불안']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>251000</v>
+        <v>87900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>221</v>
       </c>
       <c r="F15" t="n">
-        <v>484</v>
+        <v>125</v>
       </c>
       <c r="G15" t="n">
-        <v>1741</v>
+        <v>729</v>
       </c>
       <c r="H15" t="n">
-        <v>46.64</v>
+        <v>23.56</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>259500</v>
+        <v>90800</v>
       </c>
       <c r="K15" t="n">
-        <v>249500</v>
+        <v>89800</v>
       </c>
       <c r="L15" t="n">
-        <v>254500</v>
+        <v>90400</v>
       </c>
       <c r="M15" t="n">
-        <v>249000</v>
+        <v>87700</v>
       </c>
       <c r="N15" t="n">
-        <v>46.71</v>
+        <v>23.59</v>
       </c>
       <c r="O15" t="n">
-        <v>2636454357000</v>
+        <v>166877978400</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>75900</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-2691000</v>
+        <v>-546000</v>
       </c>
       <c r="S15" t="n">
-        <v>-1229000</v>
+        <v>-91000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 언급이 다수. AI 속도 조절론 및 외국인 공매도 관련 부정적 전망 존재.</t>
+          <t>국제 유가 상승에 따른 원전주 상승 가능성 언급. 공매도 평단가 대비 분석.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '공매도', '정치']</t>
+          <t>['국제유가', '원전주', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11770</v>
+        <v>251000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.72</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>478</v>
       </c>
       <c r="G16" t="n">
-        <v>86</v>
+        <v>1779</v>
       </c>
       <c r="H16" t="n">
-        <v>0.22</v>
+        <v>46.64</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>12290</v>
+        <v>259500</v>
       </c>
       <c r="K16" t="n">
-        <v>12030</v>
+        <v>249500</v>
       </c>
       <c r="L16" t="n">
-        <v>13230</v>
+        <v>254500</v>
       </c>
       <c r="M16" t="n">
-        <v>11740</v>
+        <v>249000</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9399999999999999</v>
+        <v>46.71</v>
       </c>
       <c r="O16" t="n">
-        <v>56259693655</v>
+        <v>2690537556750</v>
       </c>
       <c r="P16" t="n">
-        <v>20850</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>4020</v>
+        <v>75900</v>
       </c>
       <c r="R16" t="n">
-        <v>11000</v>
+        <v>-2691000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-1229000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
+          <t>정치적 이슈 및 시장 침체 우려로 인한 부정적 투자 심리. 외인 공매도에 대한 불신.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,143 +1923,143 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전주', '폭락', '재료 소멸']</t>
+          <t>['정치', '시장침체', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1712000</v>
+        <v>11880</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.52%</t>
+          <t>-3.34%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.08</v>
+        <v>-0.72</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="F17" t="n">
-        <v>492</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>1601</v>
+        <v>86</v>
       </c>
       <c r="H17" t="n">
-        <v>50.47</v>
+        <v>0.22</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1812000</v>
+        <v>12290</v>
       </c>
       <c r="K17" t="n">
-        <v>1707000</v>
+        <v>12030</v>
       </c>
       <c r="L17" t="n">
-        <v>1740000</v>
+        <v>13230</v>
       </c>
       <c r="M17" t="n">
-        <v>1695000</v>
+        <v>11740</v>
       </c>
       <c r="N17" t="n">
-        <v>50.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>4343182412500</v>
+        <v>56431319295</v>
       </c>
       <c r="P17" t="n">
-        <v>2987000</v>
+        <v>20850</v>
       </c>
       <c r="Q17" t="n">
-        <v>325000</v>
+        <v>4020</v>
       </c>
       <c r="R17" t="n">
-        <v>-1020000</v>
+        <v>11000</v>
       </c>
       <c r="S17" t="n">
-        <v>-202000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외국인 선물 매수 전환에도 불구하고 금리 인상 및 정치적 이슈 관련 부정적 전망 우세. 큰 폭의 하락 우려 제기.</t>
+          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['금리', '외국인', '하락']</t>
+          <t>['원전주', '폭락', '재료 소멸']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18760</v>
+        <v>1713000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.68%</t>
+          <t>-5.46%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E18" t="n">
-        <v>83</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>488</v>
       </c>
       <c r="G18" t="n">
-        <v>388</v>
+        <v>1683</v>
       </c>
       <c r="H18" t="n">
-        <v>10.55</v>
+        <v>50.47</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19890</v>
+        <v>1812000</v>
       </c>
       <c r="K18" t="n">
-        <v>19480</v>
+        <v>1707000</v>
       </c>
       <c r="L18" t="n">
-        <v>19550</v>
+        <v>1740000</v>
       </c>
       <c r="M18" t="n">
-        <v>18750</v>
+        <v>1695000</v>
       </c>
       <c r="N18" t="n">
-        <v>10.65</v>
+        <v>50.55</v>
       </c>
       <c r="O18" t="n">
-        <v>62420759585</v>
+        <v>4412411781500</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>325000</v>
       </c>
       <c r="R18" t="n">
-        <v>-480000</v>
+        <v>-1020000</v>
       </c>
       <c r="S18" t="n">
-        <v>-158000</v>
+        <v>-202000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 글이 다수. 개미 뭉치를 통한 공매도 작살 및 저점 높아지는 추세 언급.</t>
+          <t>정부 정책 및 거시경제 불확실성에 따른 투자 심리 위축. 단기 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '뭉치']</t>
+          <t>['정부정책', '거시경제', '투자심리']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13800</v>
+        <v>18750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.19%</t>
+          <t>-5.73%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>314</v>
+        <v>409</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>10.55</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,91 +2159,91 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14710</v>
+        <v>19890</v>
       </c>
       <c r="K19" t="n">
-        <v>14710</v>
+        <v>19480</v>
       </c>
       <c r="L19" t="n">
-        <v>15420</v>
+        <v>19550</v>
       </c>
       <c r="M19" t="n">
-        <v>13700</v>
+        <v>18750</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>10.65</v>
       </c>
       <c r="O19" t="n">
-        <v>28139603385</v>
+        <v>64182129635</v>
       </c>
       <c r="P19" t="n">
-        <v>19380</v>
+        <v>40350</v>
       </c>
       <c r="Q19" t="n">
-        <v>3200</v>
+        <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>-60000</v>
+        <v>-480000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-158000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>수원 파장1구역 재건축 시공사 선정 소식에도 불구하고, 부동산 시장 침체 및 외인 매도세로 주가 하락. 1만원대 지지선 약화 우려.</t>
+          <t>공매도 세력에 대한 경고와 함께 '대차해지 운동'을 통한 주가 부양 논의.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['재건축', '부동산 침체', '외인 매도']</t>
+          <t>['공매도', '대차해지', '개미뭉치']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11390</v>
+        <v>13820</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-8.51%</t>
+          <t>-6.05%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>184</v>
+        <v>322</v>
       </c>
       <c r="H20" t="n">
-        <v>17.58</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,58 +2251,150 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>12450</v>
+        <v>14710</v>
       </c>
       <c r="K20" t="n">
-        <v>11960</v>
+        <v>14710</v>
       </c>
       <c r="L20" t="n">
-        <v>13900</v>
+        <v>15420</v>
       </c>
       <c r="M20" t="n">
-        <v>11310</v>
+        <v>13700</v>
       </c>
       <c r="N20" t="n">
-        <v>17.07</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>63099342595</v>
+        <v>28369423040</v>
       </c>
       <c r="P20" t="n">
-        <v>14350</v>
+        <v>19380</v>
       </c>
       <c r="Q20" t="n">
-        <v>465</v>
+        <v>3200</v>
       </c>
       <c r="R20" t="n">
-        <v>-140000</v>
+        <v>-60000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>외국인 대량 매수 포착 및 급등주 언급. 수급 싸움 및 외인 매도 가능성도 제기.</t>
+          <t>주가 하락세 지속 및 건설 사업 수주 소식에도 불구하고 부정적 전망 우세.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['외국인', '급등주', '수급']</t>
+          <t>['주가하락', '건설사업', '부정적전망']</t>
         </is>
       </c>
       <c r="X20" t="n">
+        <v>53</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>금호전기</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>11430</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-8.19%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E21" t="n">
+        <v>90</v>
+      </c>
+      <c r="F21" t="n">
+        <v>52</v>
+      </c>
+      <c r="G21" t="n">
+        <v>195</v>
+      </c>
+      <c r="H21" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>12450</v>
+      </c>
+      <c r="K21" t="n">
+        <v>11960</v>
+      </c>
+      <c r="L21" t="n">
+        <v>13900</v>
+      </c>
+      <c r="M21" t="n">
+        <v>11310</v>
+      </c>
+      <c r="N21" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="O21" t="n">
+        <v>63380321175</v>
+      </c>
+      <c r="P21" t="n">
+        <v>14350</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>465</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-140000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>외인 대량 매수세 유입에 따른 단기 급등 기대감. 투자 경고 종목 지정 우려.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['외인매수', '급등주', '투자경고']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
         <v>1</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>001210</t>
         </is>

--- a/data/trending_integrated_20260914_13.xlsx
+++ b/data/trending_integrated_20260914_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G2" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>269618038915</v>
+        <v>269829159305</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6420</v>
+        <v>6460</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+16.52%</t>
+          <t>+17.24%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>52302187160</v>
+        <v>52426900900</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2945</v>
+        <v>2930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+13.93%</t>
+          <t>+13.35%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
         <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>3.64</v>
       </c>
       <c r="O4" t="n">
-        <v>36559476167</v>
+        <v>37055192421</v>
       </c>
       <c r="P4" t="n">
         <v>6180</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>FDA 비만 주사제 관련 기대감과 5500억 계약 건 언급. 3상 시작 전 FDA 승인 가능성 언급.</t>
+          <t>FDA 비만주사제 및 보톡스 제품 관련 긍정적 전망. 글로벌 확대 가능성, 시총 대비 재료 우수.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['FDA', '비만주사제', '계약']</t>
+          <t>['FDA', '비만 치료제', '글로벌 확대']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4325</v>
+        <v>4360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+11.76%</t>
+          <t>+12.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.45</v>
       </c>
       <c r="E5" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="F5" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="H5" t="n">
         <v>0.59</v>
@@ -886,7 +886,7 @@
         <v>1.04</v>
       </c>
       <c r="O5" t="n">
-        <v>270142025726</v>
+        <v>276434993045</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>AIDC, 6G, 광통신 기술 부각 및 광전자 급등세 영향. 5000원 안착 시 추가 상승 기대.</t>
+          <t>6G, AIDC, 광통신 기술 관련 긍정적 전망. 국책사업 선정 및 기술력 강조. 주가 급등 및 투자 경고 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AIDC', '6G', '광통신']</t>
+          <t>['광통신', 'AIDC', '6G']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9170</v>
+        <v>9220</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+10.62%</t>
+          <t>+11.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H6" t="n">
         <v>0.83</v>
@@ -978,7 +978,7 @@
         <v>0.82</v>
       </c>
       <c r="O6" t="n">
-        <v>41226363390</v>
+        <v>42212417960</v>
       </c>
       <c r="P6" t="n">
         <v>12800</v>
@@ -1044,7 +1044,7 @@
         <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H7" t="n">
         <v>1.44</v>
@@ -1070,7 +1070,7 @@
         <v>3.83</v>
       </c>
       <c r="O7" t="n">
-        <v>98788854928</v>
+        <v>99047348318</v>
       </c>
       <c r="P7" t="n">
         <v>4810</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8380</v>
+        <v>8370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.94%</t>
+          <t>+5.82%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1162,7 +1162,7 @@
         <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>68847014370</v>
+        <v>69024385960</v>
       </c>
       <c r="P8" t="n">
         <v>25050</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16930</v>
+        <v>16990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.42%</t>
+          <t>+5.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F9" t="n">
         <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H9" t="n">
         <v>2.7</v>
@@ -1254,7 +1254,7 @@
         <v>2.39</v>
       </c>
       <c r="O9" t="n">
-        <v>257574234265</v>
+        <v>258038148365</v>
       </c>
       <c r="P9" t="n">
         <v>30550</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22175</v>
+        <v>22400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.62%</t>
+          <t>+4.67%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="F10" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G10" t="n">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="H10" t="n">
         <v>28.81</v>
@@ -1337,7 +1337,7 @@
         <v>21100</v>
       </c>
       <c r="L10" t="n">
-        <v>22200</v>
+        <v>22500</v>
       </c>
       <c r="M10" t="n">
         <v>20850</v>
@@ -1346,7 +1346,7 @@
         <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>51850889950</v>
+        <v>63491732500</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대형 상선 수주 성공 및 1.6조원 규모 계약 확인. 숏커버 및 공매도 관련 논의.</t>
+          <t>대차거래 잔고 감소, 쇄빙선/LNG선/해상데이터센터 수주 관련 긍정적 분석. 숏커버 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', '상선', '공매도']</t>
+          <t>['수주', '숏커버', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14570</v>
+        <v>14670</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.97%</t>
+          <t>+3.67%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.62</v>
       </c>
       <c r="E11" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F11" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G11" t="n">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="H11" t="n">
         <v>1.88</v>
@@ -1438,7 +1438,7 @@
         <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>157357283710</v>
+        <v>159187595370</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>AI 및 광통신 기술 관련 호재 언급. 광통신 대장주 및 15000원 돌파 기대감 표출. 프로그램 매수세 확인.</t>
+          <t>AIDC, 광통신 기술 성장성 언급. GPU 확보와의 연관성. 주가 상승 기대감, 프로그램 폭풍 매수.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '프로그램매수']</t>
+          <t>['광통신', 'AIDC', 'GPU']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8520</v>
+        <v>8470</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.77%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="F12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" t="n">
-        <v>1172</v>
+        <v>1225</v>
       </c>
       <c r="H12" t="n">
         <v>0.75</v>
@@ -1530,7 +1530,7 @@
         <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>30156920885</v>
+        <v>30806094480</v>
       </c>
       <c r="P12" t="n">
         <v>21500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>글로벌 심포지엄 개최 기사 언급. 탑급 교수 발표와 항암 신약 재료 기대감.</t>
+          <t>암 치료 바이오 신약 개발 관련 긍정적 전망. 글로벌 심포지엄 개최 및 교수진 역량 강조. 시총 대비 재료 우수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['항암', '심포지엄', '신약']</t>
+          <t>['항암제', '바이오 신약', '심포지엄']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14750</v>
+        <v>14670</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.97</v>
       </c>
       <c r="E13" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F13" t="n">
         <v>156</v>
       </c>
       <c r="G13" t="n">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="H13" t="n">
         <v>1.17</v>
@@ -1622,7 +1622,7 @@
         <v>3.14</v>
       </c>
       <c r="O13" t="n">
-        <v>105912846005</v>
+        <v>106604654160</v>
       </c>
       <c r="P13" t="n">
         <v>36200</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1862</v>
+        <v>1857</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1714,7 +1714,7 @@
         <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>15831201889</v>
+        <v>15935959908</v>
       </c>
       <c r="P14" t="n">
         <v>4795</v>
@@ -1774,13 +1774,13 @@
         <v>-0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F15" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G15" t="n">
-        <v>729</v>
+        <v>751</v>
       </c>
       <c r="H15" t="n">
         <v>23.56</v>
@@ -1806,7 +1806,7 @@
         <v>23.59</v>
       </c>
       <c r="O15" t="n">
-        <v>166877978400</v>
+        <v>170695930100</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>국제 유가 상승에 따른 원전주 상승 가능성 언급. 공매도 평단가 대비 분석.</t>
+          <t>오후 반등 기대감, 국제 유가 상승에 따른 원전주 상승 가능성 언급. 프로그램/외인/기관 매도 중.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['국제유가', '원전주', '공매도']</t>
+          <t>['원전주', '국제 유가', '수급']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G16" t="n">
-        <v>1779</v>
+        <v>1771</v>
       </c>
       <c r="H16" t="n">
         <v>46.64</v>
@@ -1898,7 +1898,7 @@
         <v>46.71</v>
       </c>
       <c r="O16" t="n">
-        <v>2690537556750</v>
+        <v>2755669331500</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 시장 침체 우려로 인한 부정적 투자 심리. 외인 공매도에 대한 불신.</t>
+          <t>대통령 및 정치 관련 언급 다수, 주식 시장 전반의 부정적 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['정치', '시장침체', '공매도']</t>
+          <t>['정치', '시장 전망', '개미 투자자']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11880</v>
+        <v>11770</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.34%</t>
+          <t>-4.23%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.72</v>
       </c>
       <c r="E17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H17" t="n">
         <v>0.22</v>
@@ -1990,7 +1990,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>56431319295</v>
+        <v>56628511200</v>
       </c>
       <c r="P17" t="n">
         <v>20850</v>
@@ -2056,7 +2056,7 @@
         <v>488</v>
       </c>
       <c r="G18" t="n">
-        <v>1683</v>
+        <v>1744</v>
       </c>
       <c r="H18" t="n">
         <v>50.47</v>
@@ -2082,7 +2082,7 @@
         <v>50.55</v>
       </c>
       <c r="O18" t="n">
-        <v>4412411781500</v>
+        <v>4485251640000</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정부 정책 및 거시경제 불확실성에 따른 투자 심리 위축. 단기 급락 가능성 언급.</t>
+          <t>정부 정책 및 시장 상황에 대한 불만, 주가 하락에 대한 불안감 표출. 외인 매수 전환 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['정부정책', '거시경제', '투자심리']</t>
+          <t>['금리 인상', '시장 불확실성', '외인 선물']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18750</v>
+        <v>18730</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.73%</t>
+          <t>-5.83%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F19" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="H19" t="n">
         <v>10.55</v>
@@ -2168,13 +2168,13 @@
         <v>19550</v>
       </c>
       <c r="M19" t="n">
-        <v>18750</v>
+        <v>18720</v>
       </c>
       <c r="N19" t="n">
         <v>10.65</v>
       </c>
       <c r="O19" t="n">
-        <v>64182129635</v>
+        <v>65962276615</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 경고와 함께 '대차해지 운동'을 통한 주가 부양 논의.</t>
+          <t>대차해지 운동 독려와 개미 뭉치기 주장에도 불구하고 주가 하락세.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '개미뭉치']</t>
+          <t>['대차해지', '공매도', '개미']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13820</v>
+        <v>13790</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-6.05%</t>
+          <t>-6.25%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>28369423040</v>
+        <v>28940231810</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 하락세 지속 및 건설 사업 수주 소식에도 불구하고 부정적 전망 우세.</t>
+          <t>주가 하락세, 조정 및 계단식 하락 언급. 호재에도 불구하고 주가 부진. 수원 파장1구역 시공사 선정.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가하락', '건설사업', '부정적전망']</t>
+          <t>['주가 하락', '재건축', '시공사 선정']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11430</v>
+        <v>11370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-8.19%</t>
+          <t>-8.67%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.51</v>
       </c>
       <c r="E21" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G21" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H21" t="n">
         <v>17.58</v>
@@ -2358,7 +2358,7 @@
         <v>17.07</v>
       </c>
       <c r="O21" t="n">
-        <v>63380321175</v>
+        <v>63806513135</v>
       </c>
       <c r="P21" t="n">
         <v>14350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>외인 대량 매수세 유입에 따른 단기 급등 기대감. 투자 경고 종목 지정 우려.</t>
+          <t>외인 대량 매수 언급, 단기 급등 기대감. 거래량 증가.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['외인매수', '급등주', '투자경고']</t>
+          <t>['외국인 매수', '급등주', '거래량']</t>
         </is>
       </c>
       <c r="X21" t="n">

--- a/data/trending_integrated_20260914_13.xlsx
+++ b/data/trending_integrated_20260914_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G2" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>269829159305</v>
+        <v>269945610835</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 테마 부각, 3연상 기대감 존재.</t>
+          <t>차세대 광반도체 및 광통신 관련주로, 3연상 및 텐버거 가능성 언급. 시세 끝 조심 및 급락장 대응 필요.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', '3연상']</t>
+          <t>['광반도체', '광통신', '주포']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6460</v>
+        <v>6410</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+17.24%</t>
+          <t>+16.33%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>52426900900</v>
+        <v>52588420390</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,18 +751,18 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2930</v>
+        <v>2915</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+13.35%</t>
+          <t>+12.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
         <v>48</v>
@@ -794,7 +794,7 @@
         <v>3.64</v>
       </c>
       <c r="O4" t="n">
-        <v>37055192421</v>
+        <v>37378164882</v>
       </c>
       <c r="P4" t="n">
         <v>6180</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4360</v>
+        <v>4340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+12.66%</t>
+          <t>+12.14%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.45</v>
       </c>
       <c r="E5" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G5" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="H5" t="n">
         <v>0.59</v>
@@ -886,7 +886,7 @@
         <v>1.04</v>
       </c>
       <c r="O5" t="n">
-        <v>276434993045</v>
+        <v>278992306656</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,12 +902,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>6G, AIDC, 광통신 기술 관련 긍정적 전망. 국책사업 선정 및 기술력 강조. 주가 급등 및 투자 경고 언급.</t>
+          <t>AIDC 광통신 기술 및 6G 시대 도래에 따른 수혜 기대. 광전자와 함께 언급되며, 투자 경고에도 8000원 이상 가치 주장.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9220</v>
+        <v>9160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+11.22%</t>
+          <t>+10.49%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H6" t="n">
         <v>0.83</v>
@@ -978,7 +978,7 @@
         <v>0.82</v>
       </c>
       <c r="O6" t="n">
-        <v>42212417960</v>
+        <v>42551916640</v>
       </c>
       <c r="P6" t="n">
         <v>12800</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2800</v>
+        <v>8610</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.87%</t>
+          <t>+8.85%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-2.39</v>
+        <v>0.55</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>220</v>
+        <v>95</v>
       </c>
       <c r="H7" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2620</v>
+        <v>7910</v>
       </c>
       <c r="K7" t="n">
-        <v>2745</v>
+        <v>7800</v>
       </c>
       <c r="L7" t="n">
-        <v>3145</v>
+        <v>9840</v>
       </c>
       <c r="M7" t="n">
-        <v>2700</v>
+        <v>7540</v>
       </c>
       <c r="N7" t="n">
-        <v>3.83</v>
+        <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>99047348318</v>
+        <v>69363602945</v>
       </c>
       <c r="P7" t="n">
-        <v>4810</v>
+        <v>25050</v>
       </c>
       <c r="Q7" t="n">
-        <v>1400</v>
+        <v>3705</v>
       </c>
       <c r="R7" t="n">
-        <v>-275000</v>
+        <v>19000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
+          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자 보안', '매출액', '전고점 돌파']</t>
+          <t>['펩타이드', '특허 등록', '면역 조절']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8370</v>
+        <v>2805</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.82%</t>
+          <t>+7.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.55</v>
+        <v>-2.39</v>
       </c>
       <c r="E8" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
         <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>94</v>
+        <v>225</v>
       </c>
       <c r="H8" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7910</v>
+        <v>2620</v>
       </c>
       <c r="K8" t="n">
-        <v>7800</v>
+        <v>2745</v>
       </c>
       <c r="L8" t="n">
-        <v>9840</v>
+        <v>3145</v>
       </c>
       <c r="M8" t="n">
-        <v>7540</v>
+        <v>2700</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>3.83</v>
       </c>
       <c r="O8" t="n">
-        <v>69024385960</v>
+        <v>99323209423</v>
       </c>
       <c r="P8" t="n">
-        <v>25050</v>
+        <v>4810</v>
       </c>
       <c r="Q8" t="n">
-        <v>3705</v>
+        <v>1400</v>
       </c>
       <c r="R8" t="n">
-        <v>19000</v>
+        <v>-275000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
+          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['펩타이드', '특허 등록', '면역 조절']</t>
+          <t>['양자 보안', '매출액', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16990</v>
+        <v>17000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.79%</t>
+          <t>+5.85%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H9" t="n">
         <v>2.7</v>
@@ -1254,7 +1254,7 @@
         <v>2.39</v>
       </c>
       <c r="O9" t="n">
-        <v>258038148365</v>
+        <v>258420464790</v>
       </c>
       <c r="P9" t="n">
         <v>30550</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론에 따른 영향 및 프로그램 매도세 관찰. 2연상 기대감.</t>
+          <t>AI 개발 속도 조절론 및 트럼프 발언에 따른 변동성 발생. 보안주로서 남은 가치 언급 및 지지선 이탈 가능성 시사.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '속도조절론', '프로그램매도']</t>
+          <t>['AI', '보안주', '지지선']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22400</v>
+        <v>22350</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.67%</t>
+          <t>+4.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F10" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G10" t="n">
-        <v>350</v>
+        <v>399</v>
       </c>
       <c r="H10" t="n">
         <v>28.81</v>
@@ -1346,7 +1346,7 @@
         <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>63491732500</v>
+        <v>67121793300</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대차거래 잔고 감소, 쇄빙선/LNG선/해상데이터센터 수주 관련 긍정적 분석. 숏커버 및 공매도 관련 언급.</t>
+          <t>대형 상선 수주(1.6조원) 공시 및 숏커버/숏스퀴즈 기대. 조선업 호황 및 증권사 목표가 상향 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', '숏커버', '공매도']</t>
+          <t>['수주', '조선업', '숏커버']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14670</v>
+        <v>14580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.67%</t>
+          <t>+3.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>184</v>
       </c>
       <c r="F11" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G11" t="n">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="H11" t="n">
         <v>1.88</v>
@@ -1438,7 +1438,7 @@
         <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>159187595370</v>
+        <v>160565491920</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>AIDC, 광통신 기술 성장성 언급. GPU 확보와의 연관성. 주가 상승 기대감, 프로그램 폭풍 매수.</t>
+          <t>GPU 확보 및 AIDC 광통신 기술 관련 뉴스 언급, 기대감에도 불구하고 주가 부진에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', 'GPU']</t>
+          <t>['AIDC', '광통신', 'GPU']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8470</v>
+        <v>8530</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+2.90%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="F12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G12" t="n">
-        <v>1225</v>
+        <v>1272</v>
       </c>
       <c r="H12" t="n">
         <v>0.75</v>
@@ -1530,7 +1530,7 @@
         <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>30806094480</v>
+        <v>31097723455</v>
       </c>
       <c r="P12" t="n">
         <v>21500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>암 치료 바이오 신약 개발 관련 긍정적 전망. 글로벌 심포지엄 개최 및 교수진 역량 강조. 시총 대비 재료 우수.</t>
+          <t>암 치료 바이오 신약 관련 글로벌 심포지엄 개최 및 항암 전략 제시 뉴스 기반, 기대감 고조.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['항암제', '바이오 신약', '심포지엄']</t>
+          <t>['항암', '바이오 신약', '심포지엄']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14670</v>
+        <v>14760</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.97</v>
       </c>
       <c r="E13" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F13" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G13" t="n">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="H13" t="n">
         <v>1.17</v>
@@ -1622,7 +1622,7 @@
         <v>3.14</v>
       </c>
       <c r="O13" t="n">
-        <v>106604654160</v>
+        <v>106882663300</v>
       </c>
       <c r="P13" t="n">
         <v>36200</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H14" t="n">
         <v>2.08</v>
@@ -1714,7 +1714,7 @@
         <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>15935959908</v>
+        <v>16065740494</v>
       </c>
       <c r="P14" t="n">
         <v>4795</v>
@@ -1774,13 +1774,13 @@
         <v>-0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F15" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G15" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="H15" t="n">
         <v>23.56</v>
@@ -1806,7 +1806,7 @@
         <v>23.59</v>
       </c>
       <c r="O15" t="n">
-        <v>170695930100</v>
+        <v>172679791050</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>오후 반등 기대감, 국제 유가 상승에 따른 원전주 상승 가능성 언급. 프로그램/외인/기관 매도 중.</t>
+          <t>원전주 상승 가능성 언급. 국제 유가 상승 및 한미 정부 지원에 따른 구조적 상승 기대. 공매도 평단가 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전주', '국제 유가', '수급']</t>
+          <t>['원전', '국제유가', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>251000</v>
+        <v>250500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-3.47%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G16" t="n">
-        <v>1771</v>
+        <v>1780</v>
       </c>
       <c r="H16" t="n">
         <v>46.64</v>
@@ -1898,7 +1898,7 @@
         <v>46.71</v>
       </c>
       <c r="O16" t="n">
-        <v>2755669331500</v>
+        <v>2795475469250</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대통령 및 정치 관련 언급 다수, 주식 시장 전반의 부정적 전망.</t>
+          <t>AI 속도 조절론, 정치적 이슈 언급. 국내 주식 시장 전반에 대한 부정적 전망 및 탈출 권유.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['정치', '시장 전망', '개미 투자자']</t>
+          <t>['AI', '정치', '국내증시']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11770</v>
+        <v>11700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>-4.80%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>69</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H17" t="n">
         <v>0.22</v>
@@ -1984,13 +1984,13 @@
         <v>13230</v>
       </c>
       <c r="M17" t="n">
-        <v>11740</v>
+        <v>11680</v>
       </c>
       <c r="N17" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>56628511200</v>
+        <v>57138385170</v>
       </c>
       <c r="P17" t="n">
         <v>20850</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1713000</v>
+        <v>1709000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.46%</t>
+          <t>-5.68%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G18" t="n">
-        <v>1744</v>
+        <v>1776</v>
       </c>
       <c r="H18" t="n">
         <v>50.47</v>
@@ -2082,7 +2082,7 @@
         <v>50.55</v>
       </c>
       <c r="O18" t="n">
-        <v>4485251640000</v>
+        <v>4551420717000</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정부 정책 및 시장 상황에 대한 불만, 주가 하락에 대한 불안감 표출. 외인 매수 전환 언급.</t>
+          <t>금리 인상, 외풍, 정치적 요인에 따른 국장 약세 전망. 매도 물량 출회 및 계좌 음전 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['금리 인상', '시장 불확실성', '외인 선물']</t>
+          <t>['금리인상', '국장', '외풍']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18730</v>
+        <v>18720</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.83%</t>
+          <t>-5.88%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G19" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="H19" t="n">
         <v>10.55</v>
@@ -2168,13 +2168,13 @@
         <v>19550</v>
       </c>
       <c r="M19" t="n">
-        <v>18720</v>
+        <v>18710</v>
       </c>
       <c r="N19" t="n">
         <v>10.65</v>
       </c>
       <c r="O19" t="n">
-        <v>65962276615</v>
+        <v>67199637560</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대차해지 운동 독려와 개미 뭉치기 주장에도 불구하고 주가 하락세.</t>
+          <t>대차해지 운동 동참 권유 및 공매도 작살 가능성 언급. 저점이 높아지고 있으며, 침착한 기다림이 필요하다는 의견.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '개미']</t>
+          <t>['대차해지', '공매도', '주주운동']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13790</v>
+        <v>13780</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-6.25%</t>
+          <t>-6.32%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F20" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" t="n">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>28940231810</v>
+        <v>29168913100</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 하락세, 조정 및 계단식 하락 언급. 호재에도 불구하고 주가 부진. 수원 파장1구역 시공사 선정.</t>
+          <t>호재에도 불구하고 계단식 하락 및 주포 방향 1만원 예상. 수원 파장1구역 재건축 수주 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가 하락', '재건축', '시공사 선정']</t>
+          <t>['계단식하락', '재건축', '주포']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11370</v>
+        <v>11340</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-8.67%</t>
+          <t>-8.92%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.51</v>
       </c>
       <c r="E21" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="H21" t="n">
         <v>17.58</v>
@@ -2358,7 +2358,7 @@
         <v>17.07</v>
       </c>
       <c r="O21" t="n">
-        <v>63806513135</v>
+        <v>64217710445</v>
       </c>
       <c r="P21" t="n">
         <v>14350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>외인 대량 매수 언급, 단기 급등 기대감. 거래량 증가.</t>
+          <t>단타 및 급등주 흐름, 외인 대량 매수 중이라는 언급. 투자 경고 및 주의 필요성 시사.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['외국인 매수', '급등주', '거래량']</t>
+          <t>['단타', '외인매수', '투자경고']</t>
         </is>
       </c>
       <c r="X21" t="n">
